--- a/HORARIOS 2025 2do cuatri.xlsx
+++ b/HORARIOS 2025 2do cuatri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Desktop\FACULTAD - NO TOCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7D53BC-7B55-4A6C-BC53-08B8DA4906CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F98E57-9747-49A9-AA58-9BE8D69EF59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11310" xr2:uid="{F4593716-D229-4581-A914-F975AFE06E21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{F4593716-D229-4581-A914-F975AFE06E21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -372,19 +372,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -863,7 +863,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="24" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="17" t="s">
@@ -884,8 +884,8 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="22"/>
-      <c r="H11" s="23" t="s">
+      <c r="F11" s="25"/>
+      <c r="H11" s="21" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="2"/>
@@ -903,8 +903,8 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="22"/>
-      <c r="H12" s="24"/>
+      <c r="F12" s="25"/>
+      <c r="H12" s="22"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="13"/>
@@ -916,7 +916,7 @@
       <c r="A13" s="11">
         <v>0.70833333333333703</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="24" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -925,7 +925,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="H13" s="24"/>
+      <c r="H13" s="22"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="13"/>
@@ -937,14 +937,14 @@
       <c r="A14" s="11">
         <v>0.750000000000004</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="19"/>
       <c r="D14" s="18" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="H14" s="25"/>
+      <c r="H14" s="23"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="13"/>
@@ -956,7 +956,7 @@
       <c r="A15" s="11">
         <v>0.79166666666667096</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="3"/>
